--- a/outputs/evaluation/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7692</v>
+        <v>0.8077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5263</v>
+        <v>0.5526</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6907</v>
+        <v>0.6877</v>
       </c>
     </row>
     <row r="5">
@@ -635,16 +635,16 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +660,16 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -685,16 +685,16 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -707,19 +707,19 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -732,19 +732,19 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,16 +987,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_020</t>
+          <t>R_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_R22b</t>
+          <t>CF_M08_R16b</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5567</v>
+        <v>0.5053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1005,19 +1005,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Complete and updated documentation, with an average time for implementing updates and resolving issues not exceeding 2 hours.</t>
+          <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R_019</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1027,31 +1027,35 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Complete and updated documentation</t>
+          <t>The system should support English (verified by a translator).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CF_M08_R15</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_R16b</t>
+          <t>CF_M08_R22b</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5572</v>
+        <v>0.5566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1060,19 +1064,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The system shall be available in Spanish and English, verified by a translator.</t>
+          <t>Complete and updated documentation, with an average time for implementing updates and resolving issues not exceeding 2 hours.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1082,20 +1086,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The system should support English (verified by a translator).</t>
+          <t>Complete and updated documentation</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>CF_M08_R15</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_022</t>
+          <t>R_22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5904</v>
+        <v>0.5903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>R_021</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_021</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,103 +1330,119 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_018</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_R21c</t>
+          <t>CF_M08_R28c</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6975</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uptime monitoring demonstrating 99.9% availability and disaster recovery tests meeting the specified recovery time.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>R_017</t>
-        </is>
-      </c>
+          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Disaster recovery testing that meets the specified recovery time.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>The profile of a company can only be edited and accessible by that
+company.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>15a. Access Requirement</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_R09</t>
+          <t>CF_M08_R21c</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7093</v>
+        <v>0.7003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A company shall be able to register a product to make it visible on its public profile.</t>
+          <t>Uptime monitoring demonstrating 99.9% availability and disaster recovery tests meeting the specified recovery time.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A company must be able to register a product and have it visible on its profile/page
-public.</t>
+          <t>Disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1446,7 +1462,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.724</v>
+        <v>0.7234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,16 +1505,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_R07b</t>
+          <t>CF_M08_R09</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7454</v>
+        <v>0.7396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1512,7 +1528,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A company shall be able to modify its public profile at any time and preview it while editing.</t>
+          <t>A company shall be able to register a product to be visible on its public profile.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1529,7 +1545,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A company must be able to preview its public profile/page while editing.</t>
+          <t>A company must be able to register a product and have it visible on its profile/page
+public.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1540,136 +1557,135 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_015</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M08_R19</t>
+          <t>CF_M08_R07b</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7592</v>
+        <v>0.7452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The system must protect user information through secure authentication.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>A company shall be able to modify its public profile at any time and preview it while editing.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The system must protect the information of
-the users through the following authentication</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>15c. Privacy Requirements</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>A company must be able to preview its public profile/page while editing.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_011</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_R11</t>
+          <t>CF_M08_R19</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A user shall be able to return a product registered by a company using its routes.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+          <t>The system must protect user information through secure authentication.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A user must be able to return a product registered in a company through the
-use of its routes.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>The system must protect the information of
+the users through the following authentication</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>15c. Privacy Requirements</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_04</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M08_R03</t>
+          <t>CF_M08_R11</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8064</v>
+        <v>0.7846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1683,7 +1699,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The system shall authenticate existing users via email.</t>
+          <t>A user shall be able to return a product registered by a company using its routes.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1700,7 +1716,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The system must be able to authenticate existing users through email.</t>
+          <t>A user must be able to return a product registered in a company through the
+use of its routes.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1711,16 +1728,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_R04</t>
+          <t>CF_M08_R03</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8991</v>
+        <v>0.8064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1734,7 +1751,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The system shall allow users to log out.</t>
+          <t>The system shall authenticate existing users via email.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1751,7 +1768,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The system must allow users to log out.</t>
+          <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1762,255 +1779,246 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_014</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_R18</t>
+          <t>CF_M08_R04</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9044</v>
+        <v>0.8991</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Usability testing with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
+          <t>The system shall allow users to log out.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>R_013</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>30</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>The system must allow users to log out.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R_14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CF_M08_R18</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9046</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Usability testing with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R_13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>31</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Performance of usability tests with at least 10 representative users, achieving
 a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>CF_M08_R17</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R_010</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CF_M08_R10</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.9458</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>A company shall be able to register a route to link it to its products.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>30</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>A company must be able to register a route to link it to its products.</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CF_M08_R17</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_023</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_R26</t>
+          <t>CF_M08_R10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle an increase in the number of users and data volume.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scalability</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>A company shall be able to register a route to link it to its products.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>30</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>A company must be able to register a route to link it to its products.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CF_M08_R26</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The system must be scalable to handle an increase in the number of users and data volume.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>33</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>The system must be scalable to handle
 an increase in the number of users and volume of data</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>12 g. Scalability and Growth Requirements</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Volere</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R_016</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CF_M08_R20</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>The system must pass security audits without critical vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>R_015</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>32</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The system must pass security audits
-data without critical vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>CF_M08_R19</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_024</t>
+          <t>R_16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_R27</t>
+          <t>CF_M08_R20</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9908</v>
+        <v>0.9696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2019,19 +2027,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Capacity to increase server resources and maintain performance with a 50% increase in workload.</t>
+          <t>The system must pass security audits without critical vulnerabilities.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R_023</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2041,91 +2049,151 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>32</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The system must pass security audits
+data without critical vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CF_M08_R19</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R_24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M08_R27</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9906</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Capacity to increase server resources and maintain performance with a 50% increase in workload.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>33</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Capacity to increase the resources of the
 server and maintain performance with a
 50% increase in workload.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>CF_M08_R26</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>R_013</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R_13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>CF_M08_R17</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>The user interface must be intuitive and easy to use for non-technical users.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Usability</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Volere</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>31</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>The user interface must be intuitive and
 easy to use for non-technical users.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>11a. Ease of Use Requirements</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2138,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,13 +2268,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2885</v>
+        <v>0.2884</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_012</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2236,7 +2304,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_017</t>
+          <t>R_17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2246,7 +2314,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.</t>
+          <t>The system must have 99.9% uptime and be able to recover from failures in less than 1 hour.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2261,13 +2329,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.848</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_019</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2291,23 +2359,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6466</v>
+        <v>0.6465</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_025</t>
+          <t>R_26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that specific company.</t>
+          <t>Verify that only the company user can access their products, routes, and profile.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2322,38 +2390,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6385999999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R_026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Verify that only the company user can access their products, routes, and profile.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CF_M08_R28c</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>The profile of a company can only be edited and accessible by that
-company.</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.4491</v>
+        <v>0.449</v>
       </c>
     </row>
   </sheetData>
@@ -2367,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,16 +2457,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_025</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that specific company.</t>
+          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2422</v>
+        <v>0.2641</v>
       </c>
     </row>
     <row r="3">
@@ -2460,7 +2497,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.3066</v>
+        <v>0.3063</v>
       </c>
     </row>
     <row r="4">
@@ -2512,7 +2549,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R_011</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2521,7 +2558,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.2116</v>
+        <v>0.2115</v>
       </c>
     </row>
     <row r="6">
@@ -2543,7 +2580,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R_011</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2574,7 +2611,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R_012</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2583,7 +2620,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1951</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="8">
@@ -2613,7 +2650,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2885</v>
+        <v>0.2884</v>
       </c>
     </row>
     <row r="9">
@@ -2639,11 +2676,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The system shall be available in Spanish and English, verified by a translator.</t>
+          <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.5238</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="10">
@@ -2665,16 +2702,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R_017</t>
+          <t>R_17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.</t>
+          <t>The system must have 99.9% uptime and be able to recover from failures in less than 1 hour.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.848</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="11">
@@ -2695,7 +2732,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R_018</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2704,7 +2741,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5194</v>
+        <v>0.5174</v>
       </c>
     </row>
     <row r="12">
@@ -2725,7 +2762,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R_019</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2755,7 +2792,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R_020</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2764,7 +2801,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.5152</v>
+        <v>0.5151</v>
       </c>
     </row>
     <row r="14">
@@ -2786,7 +2823,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R_021</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2817,7 +2854,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R_021</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2826,7 +2863,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.541</v>
+        <v>0.5409</v>
       </c>
     </row>
     <row r="16">
@@ -2849,16 +2886,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R_025</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that specific company.</t>
+          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6192</v>
+        <v>0.6749000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2881,76 +2918,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R_025</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that specific company.</t>
+          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.6086</v>
+        <v>0.6633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF_M08_R28c</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The profile of a company can only be edited and accessible by that
-company.</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R_025</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that specific company.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.6385999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CF_M08_R29</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>R_012</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
         <v>0.3744</v>
       </c>
     </row>

--- a/outputs/evaluation/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7429</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6579</v>
+        <v>0.6842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7432</v>
+        <v>0.7238</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.92</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="7">
@@ -527,10 +527,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -594,19 +592,19 @@
         <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -619,19 +617,19 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -644,19 +642,19 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -681,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -706,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -719,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>9</v>
@@ -731,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -741,22 +739,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +800,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +810,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -822,7 +820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +830,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,7 +947,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_02b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -958,7 +956,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5072</v>
+        <v>0.5604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -972,7 +970,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
+          <t>The system interface shall be available in English, verified by a translator.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -982,7 +980,11 @@
           <t>R_01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1003,21 +1005,25 @@
           <t>CF_M08_R15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_20b</t>
+          <t>R_02a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_R23</t>
+          <t>CF_M08_R16a</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5593</v>
+        <v>0.5604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,57 +1032,65 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Average time for implementation of updates and troubleshooting not exceeding 2 hours.</t>
+          <t>The system interface shall be available in Spanish, verified by a translator.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_19</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>R_01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Average implementation time of updates and error fixes no more than 2 hours.</t>
+          <t>The system should support Spanish (verified by a translator).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CF_M08_R22a</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>CF_M08_R15</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>R_20b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_R25b</t>
+          <t>CF_M08_R23</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5946</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,40 +1099,44 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Compatibility tests demonstrating functionality in major browsers and mobile devices.</t>
+          <t>Average time for implementation of updates and troubleshooting must not exceed 2 hours.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>R_21</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>R_19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Evidence of compatibility that they demonstrate functionality in the mobile devices (mobile phones and tablets).</t>
+          <t>Average implementation time of updates and error fixes no more than 2 hours.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R22a</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -1126,47 +1144,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>R_22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M08_R25b</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Compatibility tests demonstrating functionality in major browsers and mobile devices.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>R_21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M08_R24a</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5968</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>14c. Adaptability</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1174,87 +1188,102 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common web browsers.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>14c. Adaptability requirements</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>Evidence of compatibility that they demonstrate functionality in the mobile devices (mobile phones and tablets).</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CF_M08_R24b</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_R02</t>
+          <t>CF_M08_R24a</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.5969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The system shall allow registering new users.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>14c. Adaptability</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>The system must allow new users to register in the system.</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>The system must be compatible with the most common web browsers.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14c. Adaptability requirements</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_06</t>
+          <t>R_08a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_R05</t>
+          <t>CF_M08_R08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6488</v>
+        <v>0.612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,13 +1297,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The system shall allow logged-in users to view company profiles and their products.</t>
+          <t>A company shall have access to a dashboard to use internal functionalities.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1285,7 +1318,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
+          <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1296,84 +1329,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_25</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_R28c</t>
+          <t>CF_M08_R05</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6915</v>
+        <v>0.6465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>15a. Access Control</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system shall allow logged-in users to view company profiles and their products.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The profile of a company can only be edited and accessible by that
-company.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>15a. Access Requirement</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_08</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_R08</t>
+          <t>CF_M08_R02</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7258</v>
+        <v>0.6515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1387,7 +1403,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A company shall have access to a dashboard to use internal functionalities and view additional information.</t>
+          <t>The system shall allow registering new users.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1404,8 +1420,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A company must have access to the system dashboard to be able to use the different ones
-internal functionalities and additional information (statistics, values, etc.).</t>
+          <t>The system must allow new users to register in the system.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1416,68 +1431,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_R09</t>
+          <t>CF_M08_R28c</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7461</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A company shall be able to register a product to be visible on its public profile.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15a. Access Control</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A company must be able to register a product and have it visible on its profile/page
-public.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>The profile of a company can only be edited and accessible by that company.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>15a. Access Requirement</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_R07b</t>
+          <t>CF_M08_R09</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7486</v>
+        <v>0.7421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1525,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A company shall be able to modify its public profile at any time and preview it while editing.</t>
+          <t>A company shall be able to register a product to be visible on its public profile.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1508,7 +1542,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A company must be able to preview its public profile/page while editing.</t>
+          <t>A company must be able to register a product and have it visible on its profile/page public.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1528,7 +1562,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7644</v>
+        <v>0.7937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1567,8 +1601,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The system must protect the information of
-the users through the following authentication</t>
+          <t>The system must protect the information of the users through the following authentication.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1596,7 +1629,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.792</v>
+        <v>0.8013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1627,8 +1660,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A user must be able to return a product registered in a company through the
-use of its routes.</t>
+          <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1648,7 +1680,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8089</v>
+        <v>0.8111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1690,162 +1722,173 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_18b</t>
+          <t>R_07a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_R21c</t>
+          <t>CF_M08_R07a</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9012</v>
+        <v>0.8388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Disaster recovery tests meeting the specified recovery time.</t>
+          <t>A company shall be able to modify its public profile at any time.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>R_17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Disaster recovery testing that meets the specified recovery time.</t>
+          <t>A company must be able to modify its public profile/page at any time.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_14</t>
+          <t>R_07b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_R18</t>
+          <t>CF_M08_R07b</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9058</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Usability testing with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
+          <t>A company shall be able to preview its public profile while editing.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>R_13</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Performance of usability tests with at least 10 representative users, achieving
-a minimum satisfaction score of 8/10.</t>
+          <t>A company must be able to preview its public profile/page while editing.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>CF_M08_R17</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_18b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_R04</t>
+          <t>CF_M08_R21c</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9065</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The system shall allow users to log out.</t>
+          <t>Disaster recovery tests meeting the specified recovery time.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The system must allow users to log out.</t>
+          <t>Disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1856,16 +1899,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_18a</t>
+          <t>R_14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_R21b</t>
+          <t>CF_M08_R18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1874,19 +1917,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Uptime monitoring demonstrating 99.9% uptime.</t>
+          <t>Usability testing with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1896,275 +1939,271 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
+          <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CF_M08_R17</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_10</t>
+          <t>R_18a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_R10</t>
+          <t>CF_M08_R21b</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9515</v>
+        <v>0.9104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A company shall be able to register a route to link it to its products.</t>
+          <t>Uptime monitoring demonstrating 99.9% uptime.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A company must be able to register a route to link it to its products.</t>
+          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_R26</t>
+          <t>CF_M08_R04</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9522</v>
+        <v>0.9161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle an increase in the number of users and data volume.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>12g. Scalability</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system shall allow users to log out.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle
-an increase in the number of users and volume of data</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>12 g. Scalability and Growth Requirements</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system must allow users to log out.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_16</t>
+          <t>R_23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_R20</t>
+          <t>CF_M08_R26</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9697</v>
+        <v>0.9522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The system must pass security audits without critical vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
+          <t>The system must be scalable to handle an increase in the number of users and data volume.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>12g. Scalability</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The system must pass security audits
-data without critical vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>CF_M08_R19</t>
-        </is>
-      </c>
+          <t>The system must be scalable to handle an increase in the number of users and volume of data</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>12 g. Scalability and Growth Requirements</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_24</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_R27</t>
+          <t>CF_M08_R10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9909</v>
+        <v>0.9569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Capacity to increase server resources and maintain performance with a 50% increase in workload.</t>
+          <t>A company shall be able to register a route to link it to its products.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R_23</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Capacity to increase the resources of the
-server and maintain performance with a
-50% increase in workload.</t>
+          <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CF_M08_R26</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R_19a</t>
+          <t>R_16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_R22a</t>
+          <t>CF_M08_R20</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.9696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2174,20 +2213,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The system must be easy to maintain and update.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>14a. Maintainability</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>The system must pass security audits without critical vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>R_15</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -2199,91 +2234,86 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>The system must be easy to maintain and update.</t>
+          <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CF_M08_R19</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R_13</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_R17</t>
+          <t>CF_M08_R27</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>The user interface must be intuitive and easy to use for non-technical users.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>11a. Usability</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Capacity to increase server resources and maintain performance with a 50% increase in workload.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The user interface must be intuitive and
-easy to use for non-technical users.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>11a. Ease of Use Requirements</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CF_M08_R26</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R_20a</t>
+          <t>R_17b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_R22b</t>
+          <t>CF_M08_R21a</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2291,7 +2321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2301,17 +2331,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Complete and updated documentation.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>R_19</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>The system must be able to recover from failures in less than 1 hour.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>12e. Fault Tolerance</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2322,23 +2360,27 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Complete and updated documentation</t>
+          <t>The system must be able to recover from failures in less than 1 hour.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R_17b</t>
+          <t>R_13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_R21a</t>
+          <t>CF_M08_R17</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2351,17 +2393,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>The system must be able to recover from failures in less than 1 hour.</t>
+          <t>The user interface must be intuitive and easy to use for non-technical users.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12e. Fault Tolerance</t>
+          <t>11a. Usability</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2373,22 +2415,96 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>The system must be able to recover from failures
-in less than 1 hour.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>The user interface must be intuitive and easy to use for non-technical users.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>11a. Ease of Use Requirements</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R_19a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CF_M08_R22a</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The system must be easy to maintain and update.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>14a. Maintainability</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>32</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>The system must be easy to maintain and update.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2401,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2439,7 +2555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_01a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2449,7 +2565,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The system shall be available in both Spanish and English.</t>
+          <t>The system shall be available in Spanish.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2463,13 +2579,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3029</v>
+        <v>0.3546</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_01b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2479,149 +2595,147 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
+          <t>The system shall be available in English.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_R29</t>
+          <t>CF_M08_R15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
+          <t>The system must be available in different languages</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.3756</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_17a</t>
+          <t>R_08b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime.</t>
+          <t>A company shall have access to a dashboard to view additional information.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M08_R21b</t>
+          <t>CF_M08_R08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
+          <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.654</v>
+        <v>0.5712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_19b</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The system must have clear and complete documentation.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M08_R22b</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Complete and updated documentation</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6456</v>
+        <v>0.3764</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify that only the company user can access their products/routes/profile.</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M08_R28a</t>
+          <t>CF_M08_R21b</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.417</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_19b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The system shall use Blockchain technology to ensure transparency and traceability.</t>
+          <t>The system must have clear and complete documentation.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_R16a</t>
+          <t>CF_M08_R22b</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The system should support Spanish (verified by a translator).</t>
+          <t>Complete and updated documentation</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1009</v>
+        <v>0.6655</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2631,53 +2745,81 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The system architecture shall be based on microservices.</t>
+          <t>The system shall use Blockchain technology to ensure transparency and traceability.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R16a</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common mobile devices.</t>
+          <t>The system should support Spanish (verified by a translator).</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1471</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>R_28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The system architecture shall be based on microservices.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M08_R24b</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The system must be compatible with the most common mobile devices.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>R_29</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Constraint</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>The system shall use Amazon EC2 instances managed by Docker.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>CF_M08_R06</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>The system must be able to save all the images of all the products and users of the
-system.</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1113</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The system must be able to save all the images of all the products and users of the system.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1074</v>
       </c>
     </row>
   </sheetData>
@@ -2691,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2753,7 +2895,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2518</v>
+        <v>0.2433</v>
       </c>
     </row>
     <row r="3">
@@ -2769,8 +2911,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The system must be able to save all the images of all the products and users of the
-system.</t>
+          <t>The system must be able to save all the images of all the products and users of the system.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2784,13 +2925,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.3008</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_R07a</t>
+          <t>CF_M08_R12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2800,27 +2941,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A company must be able to modify its public profile/page at any time.</t>
+          <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A company shall be able to modify its public profile at any time and preview it while editing.</t>
+          <t>A user shall be able to return a product registered by a company using its routes.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6103</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_R12</t>
+          <t>CF_M08_R13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2830,8 +2971,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Every product must have a predetermined route in which the user returns it
-on his own account and with his own means.</t>
+          <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2845,13 +2985,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.2157</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_R13</t>
+          <t>CF_M08_R14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2861,130 +3001,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Every route must have an associated budget (can be 0) which the user must
-be able to pay using the system when returning the product.</t>
+          <t>The system must have a membership system/plans for companies that want to have certain advantages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A user shall be able to return a product registered by a company using its routes.</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.3147</v>
+        <v>0.2052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_R14</t>
+          <t>CF_M08_R15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The system must have a membership system/plans for companies that want to
-have certain advantages.</t>
+          <t>The system must be available in different languages</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R_17a</t>
+          <t>R_01a</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime.</t>
+          <t>The system shall be available in Spanish.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.2121</v>
+        <v>0.3546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_R15</t>
+          <t>CF_M08_R22b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The system must be available in different languages</t>
+          <t>Complete and updated documentation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_19b</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The system shall be available in both Spanish and English.</t>
+          <t>The system must have clear and complete documentation.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.3029</v>
+        <v>0.6655</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_R16a</t>
+          <t>CF_M08_R24b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The system should support Spanish (verified by a translator).</t>
+          <t>The system must be compatible with the most common mobile devices.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
+          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.4777</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R25a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common mobile devices.</t>
+          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge).</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2998,44 +3135,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_R25a</t>
+          <t>CF_M08_R28a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox,
-Safari, Edge).</t>
+          <t>The products of a company can only be edited and accessible by that company.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5402</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M08_R28a</t>
+          <t>CF_M08_R28b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3045,9 +3181,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>The routes of a company can only be edited and accessible by that company.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3061,69 +3195,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6581</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M08_R28b</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The routes of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R_25</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.6304</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M08_R29</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.3756</v>
+        <v>0.3764</v>
       </c>
     </row>
   </sheetData>
